--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-AtElgaEmedValueSetATC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
